--- a/Kinto_SaaS_Multitenancy_Plan.xlsx
+++ b/Kinto_SaaS_Multitenancy_Plan.xlsx
@@ -11,13 +11,14 @@
     <sheet sheetId="5" name="Implementation Phases" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="SaaS &amp; Deployment" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Integrations Impact" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Customization Pricing" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="398">
   <si>
     <t>KINTO SMART OPS — MULTITENANCY &amp; SAAS PLAN</t>
   </si>
@@ -673,7 +674,7 @@
     <t>Grace period begins. Read-only mode.</t>
   </si>
   <si>
-    <t>Day 1-7</t>
+    <t>Day 1–7</t>
   </si>
   <si>
     <t>User can view all data but cannot create new records. Reminder emails sent.</t>
@@ -685,7 +686,7 @@
     <t>Account suspended. Login blocked. Data fully preserved.</t>
   </si>
   <si>
-    <t>Day 8-90</t>
+    <t>Day 8–90</t>
   </si>
   <si>
     <t>Data retained. Reactivate anytime by renewing subscription.</t>
@@ -721,7 +722,7 @@
     <t>Days</t>
   </si>
   <si>
-    <t>Cumulative</t>
+    <t>Cumul.</t>
   </si>
   <si>
     <t>Priority</t>
@@ -808,7 +809,7 @@
     <t>Cross-tenant data leak tests. Module enforcement tests. Billing flow tests. Load testing. Security audit. UAT with KINTO.</t>
   </si>
   <si>
-    <t>TOTAL ESTIMATED EFFORT: ~33–36 working days  |  ~7–8 weeks  |  Timeline depends on parallel development capacity</t>
+    <t>TOTAL ESTIMATED EFFORT: ~33–36 working days  |  ~7–8 weeks</t>
   </si>
   <si>
     <t>WHAT STAYS EXACTLY THE SAME (ZERO CHANGES)</t>
@@ -868,7 +869,7 @@
     <t>AWS EC2 + RDS (Mumbai region)</t>
   </si>
   <si>
-    <t>More control. Indian data residency. Cost-effective at scale. No code change except file storage.</t>
+    <t>More control. Indian data residency. Cost-effective at scale.</t>
   </si>
   <si>
     <t>₹8,000–20,000/mo</t>
@@ -907,72 +908,60 @@
     <t>No EC2, no Docker, no Linux, no DevOps needed</t>
   </si>
   <si>
-    <t>CODE CHANGES NEEDED FOR CLOUD (AWS/GCP) — only if moving beyond Replit</t>
-  </si>
-  <si>
-    <t>Component</t>
-  </si>
-  <si>
-    <t>Change Required</t>
-  </si>
-  <si>
-    <t>Easy</t>
+    <t>SAAS BUSINESS MODEL</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>= SaaS Vendor. Your company uses the system for free as Tenant 1.</t>
+  </si>
+  <si>
+    <t>= Manufacturing companies paying monthly subscriptions.</t>
+  </si>
+  <si>
+    <t>MRR (Monthly Recurring Revenue) from all active tenants.</t>
+  </si>
+  <si>
+    <t>Customers sign up, complete wizard, start 14-day trial, choose plan, pay via Razorpay.</t>
+  </si>
+  <si>
+    <t>Starter → Professional → Enterprise as companies grow.</t>
+  </si>
+  <si>
+    <t>Razorpay supports UPI, NEFT, credit/debit cards — best for Indian B2B.</t>
+  </si>
+  <si>
+    <t>Offer 2 months free on annual plan to encourage commitment.</t>
+  </si>
+  <si>
+    <t>50 tenants or 500 tenants — same codebase, same Replit deployment until you need more.</t>
+  </si>
+  <si>
+    <t>INTEGRATIONS &amp; SERVICES IMPACT</t>
+  </si>
+  <si>
+    <t>WhatsApp  |  Email  |  Files  |  Reports  |  API</t>
+  </si>
+  <si>
+    <t>WHATSAPP INTEGRATION</t>
+  </si>
+  <si>
+    <t>Aspect</t>
+  </si>
+  <si>
+    <t>Current</t>
+  </si>
+  <si>
+    <t>After Multitenancy</t>
+  </si>
+  <si>
+    <t>Credentials</t>
   </si>
   <si>
     <t>Low</t>
   </si>
   <si>
-    <t>SAAS BUSINESS MODEL</t>
-  </si>
-  <si>
-    <t>Item</t>
-  </si>
-  <si>
-    <t>= SaaS Vendor. Your company uses the system for free as Tenant 1.</t>
-  </si>
-  <si>
-    <t>= Manufacturing companies paying monthly subscriptions.</t>
-  </si>
-  <si>
-    <t>MRR (Monthly Recurring Revenue) from all active tenants.</t>
-  </si>
-  <si>
-    <t>Customers sign up, complete wizard, start 14-day trial, choose plan, pay via Razorpay.</t>
-  </si>
-  <si>
-    <t>Starter → Professional → Enterprise as companies grow.</t>
-  </si>
-  <si>
-    <t>Razorpay supports UPI, NEFT, credit/debit cards — best for Indian B2B.</t>
-  </si>
-  <si>
-    <t>Offer 2 months free on annual plan to encourage commitment.</t>
-  </si>
-  <si>
-    <t>50 tenants or 500 tenants — same codebase, same Replit deployment until you need more.</t>
-  </si>
-  <si>
-    <t>INTEGRATIONS &amp; SERVICES IMPACT</t>
-  </si>
-  <si>
-    <t>WhatsApp  |  Email  |  Files  |  Reports  |  API</t>
-  </si>
-  <si>
-    <t>WHATSAPP INTEGRATION</t>
-  </si>
-  <si>
-    <t>Aspect</t>
-  </si>
-  <si>
-    <t>Current</t>
-  </si>
-  <si>
-    <t>After Multitenancy</t>
-  </si>
-  <si>
-    <t>Credentials</t>
-  </si>
-  <si>
     <t>Incoming webhook</t>
   </si>
   <si>
@@ -982,36 +971,27 @@
     <t>Checklist completion</t>
   </si>
   <si>
-    <t>Tenant without own number</t>
+    <t>EMAIL NOTIFICATIONS</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>Sender name</t>
+  </si>
+  <si>
+    <t>Reply-to</t>
+  </si>
+  <si>
+    <t>Email logo</t>
+  </si>
+  <si>
+    <t>Machine reminders</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>EMAIL NOTIFICATIONS</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>Sender name</t>
-  </si>
-  <si>
-    <t>Reply-to</t>
-  </si>
-  <si>
-    <t>Email logo</t>
-  </si>
-  <si>
-    <t>Machine startup reminders</t>
-  </si>
-  <si>
-    <t>None (auto via tenant_id)</t>
-  </si>
-  <si>
-    <t>Missed checklist alerts</t>
-  </si>
-  <si>
     <t>Document expiry alerts</t>
   </si>
   <si>
@@ -1042,6 +1022,9 @@
     <t>Report</t>
   </si>
   <si>
+    <t>Change</t>
+  </si>
+  <si>
     <t>All operational reports</t>
   </si>
   <si>
@@ -1060,14 +1043,182 @@
     <t>Super Admin MRR report</t>
   </si>
   <si>
-    <t>Super Admin storage report</t>
+    <t>CUSTOMIZATION PRICING</t>
+  </si>
+  <si>
+    <t>Fixed Price Model  |  One Clear Rate  |  No Hourly Billing</t>
+  </si>
+  <si>
+    <t>RULE: All customizations are Fixed Price only. Quote upfront. Customer approves before work starts. No hourly billing. No ambiguity.</t>
+  </si>
+  <si>
+    <t>CUSTOMIZATION PRICE LIST</t>
+  </si>
+  <si>
+    <t>Customization Type</t>
+  </si>
+  <si>
+    <t>Min Price</t>
+  </si>
+  <si>
+    <t>Max Price</t>
+  </si>
+  <si>
+    <t>What It Includes</t>
+  </si>
+  <si>
+    <t>Custom Report</t>
+  </si>
+  <si>
+    <t>₹5,000</t>
+  </si>
+  <si>
+    <t>₹15,000</t>
+  </si>
+  <si>
+    <t>New Excel or PDF report specific to one customer — layout, data, columns as per their requirement</t>
+  </si>
+  <si>
+    <t>Custom Fields in a Module</t>
+  </si>
+  <si>
+    <t>₹3,000</t>
+  </si>
+  <si>
+    <t>₹8,000</t>
+  </si>
+  <si>
+    <t>Additional fields not in standard forms — invoices, production, checklist, etc.</t>
+  </si>
+  <si>
+    <t>Custom Workflow / Approval Flow</t>
+  </si>
+  <si>
+    <t>₹10,000</t>
+  </si>
+  <si>
+    <t>₹30,000</t>
+  </si>
+  <si>
+    <t>Different approval stages, state changes, rules or conditions specific to one customer</t>
+  </si>
+  <si>
+    <t>API / Tally / ERP Integration</t>
+  </si>
+  <si>
+    <t>₹50,000</t>
+  </si>
+  <si>
+    <t>Connect Kinto with customer's existing Tally, ERP, or third-party software via API</t>
+  </si>
+  <si>
+    <t>WhatsApp Custom Flow</t>
+  </si>
+  <si>
+    <t>₹20,000</t>
+  </si>
+  <si>
+    <t>Custom bot messages, custom checklist templates, custom reminder logic for WhatsApp</t>
+  </si>
+  <si>
+    <t>Custom MIS Dashboard</t>
+  </si>
+  <si>
+    <t>₹25,000</t>
+  </si>
+  <si>
+    <t>New MIS widgets, KPIs, charts or analytics screens specific to customer's operations</t>
+  </si>
+  <si>
+    <t>Data Migration (Historical Import)</t>
+  </si>
+  <si>
+    <t>Import customer's historical data from Excel, Tally, or other software into Kinto</t>
+  </si>
+  <si>
+    <t>Training Session</t>
+  </si>
+  <si>
+    <t>Per session — on-site or remote training for customer's team (per session rate)</t>
+  </si>
+  <si>
+    <t>Priority Support SLA (Monthly)</t>
+  </si>
+  <si>
+    <t>₹2,000/mo</t>
+  </si>
+  <si>
+    <t>₹5,000/mo</t>
+  </si>
+  <si>
+    <t>Guaranteed response time add-on (e.g. 4-hour response). Billed monthly on top of subscription.</t>
+  </si>
+  <si>
+    <t>THE PROCESS — HOW EVERY CUSTOMIZATION WORKS</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Who Does It</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Kinto team</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>WHAT IS INCLUDED IN SUBSCRIPTION (NO EXTRA CHARGE)</t>
+  </si>
+  <si>
+    <t>Standard features available to all tenants on their plan</t>
+  </si>
+  <si>
+    <t>Bug fixes and error corrections in existing functionality</t>
+  </si>
+  <si>
+    <t>New platform features released by Kinto to all tenants (everyone gets them automatically)</t>
+  </si>
+  <si>
+    <t>Configuration within the app — roles, permissions, categories, expense types, chart of accounts, etc.</t>
+  </si>
+  <si>
+    <t>Email and WhatsApp support for how-to questions within standard usage</t>
+  </si>
+  <si>
+    <t>KEY RULE: STANDARD vs CUSTOM</t>
+  </si>
+  <si>
+    <t>If a customization built for one customer is useful to all customers → add it to the standard platform (free for everyone, grows the product). If it is specific only to that one customer → charge separately and maintain it as their private feature.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1141,6 +1292,17 @@
     <font>
       <b/>
       <color rgb="FF1E293B"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF14532D"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF78350F"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1251,7 +1413,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1358,6 +1520,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3986,7 +4157,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4222,31 +4393,33 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
-    <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
         <v>297</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>298</v>
+        <v>10</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>91</v>
       </c>
@@ -4257,173 +4430,88 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="4" t="s">
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B30" s="8" t="s">
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="C30" s="8"/>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="8"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B31" s="4" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>306</v>
-      </c>
-      <c r="C32" s="8"/>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="8"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>308</v>
-      </c>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>310</v>
-      </c>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
+      <c r="G28" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="26">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -4441,22 +4529,15 @@
     <mergeCell ref="B16:G16"/>
     <mergeCell ref="B17:G17"/>
     <mergeCell ref="A19:G19"/>
-    <mergeCell ref="B20:F20"/>
-    <mergeCell ref="B21:F21"/>
-    <mergeCell ref="B22:F22"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="B24:F24"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B20:G20"/>
+    <mergeCell ref="B21:G21"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B23:G23"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="B27:G27"/>
     <mergeCell ref="B28:G28"/>
-    <mergeCell ref="B29:G29"/>
-    <mergeCell ref="B30:G30"/>
-    <mergeCell ref="B31:G31"/>
-    <mergeCell ref="B32:G32"/>
-    <mergeCell ref="B33:G33"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4465,7 +4546,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4476,7 +4557,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4487,7 +4568,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4498,7 +4579,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4509,13 +4590,13 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
@@ -4526,10 +4607,10 @@
         <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -4540,7 +4621,7 @@
         <v>91</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C6" s="8" t="s">
         <v>256</v>
@@ -4554,10 +4635,10 @@
         <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
@@ -4568,186 +4649,186 @@
         <v>91</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
     </row>
-    <row r="9" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B9" s="4" t="s">
+    <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C14" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+    </row>
+    <row r="15" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>322</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-    </row>
-    <row r="11" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="C15" s="8" t="s">
         <v>323</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>324</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="C16" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+    </row>
+    <row r="17" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>325</v>
       </c>
-      <c r="C13" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-    </row>
-    <row r="14" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="8" t="s">
+      <c r="C17" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="8" t="s">
-        <v>300</v>
-      </c>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="4" t="s">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B16" s="8" t="s">
+      <c r="C21" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+    </row>
+    <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="C16" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>331</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>329</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
+      <c r="C22" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -4758,10 +4839,10 @@
         <v>91</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
@@ -4772,77 +4853,77 @@
         <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>300</v>
+        <v>313</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="26" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-    </row>
-    <row r="27" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>340</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>316</v>
-      </c>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
+    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+    </row>
+    <row r="30" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -4853,10 +4934,10 @@
         <v>91</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="8"/>
@@ -4867,10 +4948,10 @@
         <v>91</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -4881,59 +4962,17 @@
         <v>91</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>322</v>
+        <v>256</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
       <c r="F34" s="8"/>
     </row>
-    <row r="35" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-    </row>
-    <row r="37" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="31">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -4942,32 +4981,512 @@
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
     <mergeCell ref="C8:F8"/>
-    <mergeCell ref="C9:F9"/>
-    <mergeCell ref="A11:G11"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C19:F19"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C20:F20"/>
+    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="C29:F29"/>
     <mergeCell ref="C30:F30"/>
     <mergeCell ref="C31:F31"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C33:F33"/>
     <mergeCell ref="C34:F34"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C36:F36"/>
-    <mergeCell ref="C37:F37"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G35"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="35" customWidth="1"/>
+    <col min="2" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="5" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+    </row>
+    <row r="5" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>349</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>351</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>352</v>
+      </c>
+      <c r="E7" s="27"/>
+      <c r="F7" s="27"/>
+      <c r="G7" s="27"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="31"/>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>358</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>359</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="27"/>
+      <c r="F9" s="27"/>
+      <c r="G9" s="27"/>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="30" t="s">
+        <v>361</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>351</v>
+      </c>
+      <c r="C10" s="29" t="s">
+        <v>362</v>
+      </c>
+      <c r="D10" s="31" t="s">
+        <v>363</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>364</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>366</v>
+      </c>
+      <c r="E11" s="27"/>
+      <c r="F11" s="27"/>
+      <c r="G11" s="27"/>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="30" t="s">
+        <v>367</v>
+      </c>
+      <c r="B12" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="C12" s="29" t="s">
+        <v>368</v>
+      </c>
+      <c r="D12" s="31" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="31"/>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>370</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>350</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>365</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>371</v>
+      </c>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="30" t="s">
+        <v>372</v>
+      </c>
+      <c r="B14" s="29" t="s">
+        <v>354</v>
+      </c>
+      <c r="C14" s="29" t="s">
+        <v>355</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>374</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>375</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>376</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>377</v>
+      </c>
+      <c r="E15" s="27"/>
+      <c r="F15" s="27"/>
+      <c r="G15" s="27"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+    </row>
+    <row r="18" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="D22" s="8"/>
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="8"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>387</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
+        <v>390</v>
+      </c>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="39"/>
+      <c r="G27" s="39"/>
+    </row>
+    <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
+        <v>392</v>
+      </c>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+    </row>
+    <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>394</v>
+      </c>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" s="4"/>
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="34" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" ht="40" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="40" t="s">
+        <v>397</v>
+      </c>
+      <c r="B35" s="40"/>
+      <c r="C35" s="40"/>
+      <c r="D35" s="40"/>
+      <c r="E35" s="40"/>
+      <c r="F35" s="40"/>
+      <c r="G35" s="40"/>
+    </row>
+  </sheetData>
+  <mergeCells count="31">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="A17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="C24:G24"/>
+    <mergeCell ref="C25:G25"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A35:G35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Kinto_SaaS_Multitenancy_Plan.xlsx
+++ b/Kinto_SaaS_Multitenancy_Plan.xlsx
@@ -12,13 +12,15 @@
     <sheet sheetId="6" name="SaaS &amp; Deployment" state="visible" r:id="rId9"/>
     <sheet sheetId="7" name="Integrations Impact" state="visible" r:id="rId10"/>
     <sheet sheetId="8" name="Customization Pricing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Pitch Deck" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Digital Marketing" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="521">
   <si>
     <t>KINTO SMART OPS — MULTITENANCY &amp; SAAS PLAN</t>
   </si>
@@ -155,7 +157,7 @@
     <t>tenant_billing_invoices</t>
   </si>
   <si>
-    <t>id, tenant_id, period_month, amount_paise, gst_paise, status (draft/sent/paid/overdue), due_date, paid_at</t>
+    <t>id, tenant_id, period_month, amount_paise, gst_paise, status, due_date, paid_at</t>
   </si>
   <si>
     <t>tenant_billing_payments</t>
@@ -290,13 +292,13 @@
     <t>mis_snapshots</t>
   </si>
   <si>
-    <t>DEFAULT TENANT (inserted before migration runs)</t>
+    <t>DEFAULT TENANT</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>id=1  |  name="KINTO Operations"  |  slug="kinto"  |  status="active"  |  All existing users → tenant_id=1  |  All existing data → tenant_id=1</t>
+    <t>id=1  |  name="KINTO Operations"  |  slug="kinto"  |  status="active"  |  All existing users → tenant_id=1</t>
   </si>
   <si>
     <t>AUTHENTICATION &amp; SESSION DESIGN</t>
@@ -323,22 +325,22 @@
     <t>System checks: find all tenants where these credentials are valid</t>
   </si>
   <si>
-    <t>Result A</t>
-  </si>
-  <si>
-    <t>1 tenant found → login directly, no extra screen shown</t>
-  </si>
-  <si>
-    <t>Result B</t>
-  </si>
-  <si>
-    <t>2+ tenants found → show "Select Your Company" picker screen</t>
-  </si>
-  <si>
-    <t>Result C</t>
-  </si>
-  <si>
-    <t>0 matches → show "Invalid credentials" (unchanged)</t>
+    <t>1 tenant found</t>
+  </si>
+  <si>
+    <t>Login directly — no extra screen shown</t>
+  </si>
+  <si>
+    <t>2+ tenants found</t>
+  </si>
+  <si>
+    <t>Show "Select Your Company" picker screen</t>
+  </si>
+  <si>
+    <t>0 matches</t>
+  </si>
+  <si>
+    <t>Show "Invalid credentials" (unchanged)</t>
   </si>
   <si>
     <t>After login</t>
@@ -347,13 +349,13 @@
     <t>Session stores: userId, tenantId, role, tenantSlug, tenantName, planFlags</t>
   </si>
   <si>
-    <t>SESSION OBJECT (after login)</t>
-  </si>
-  <si>
-    <t>Session Key</t>
-  </si>
-  <si>
-    <t>Example Value</t>
+    <t>SESSION OBJECT</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Example</t>
   </si>
   <si>
     <t>Description</t>
@@ -383,7 +385,7 @@
     <t>"manager"</t>
   </si>
   <si>
-    <t>Their role in THIS tenant (can differ per tenant)</t>
+    <t>Their role in THIS tenant</t>
   </si>
   <si>
     <t>tenantSlug</t>
@@ -410,63 +412,33 @@
     <t>true/false</t>
   </si>
   <si>
-    <t>Whether tenant's plan includes WhatsApp module</t>
+    <t>WhatsApp module access</t>
   </si>
   <si>
     <t>planFlags.hasProduction</t>
   </si>
   <si>
-    <t>Whether tenant's plan includes BOM / Production</t>
+    <t>BOM / Production access</t>
   </si>
   <si>
     <t>planFlags.hasMis</t>
   </si>
   <si>
-    <t>Whether tenant's plan includes MIS Analytics</t>
-  </si>
-  <si>
-    <t>planFlags.hasAccounting</t>
-  </si>
-  <si>
-    <t>Whether tenant's plan includes Accounting</t>
-  </si>
-  <si>
-    <t>MULTI-COMPANY SUPPORT</t>
+    <t>MIS Analytics access</t>
+  </si>
+  <si>
+    <t>LICENSING &amp; PLAN STRUCTURE</t>
+  </si>
+  <si>
+    <t>Subscription Tiers  |  Enforcement  |  Grace Period</t>
+  </si>
+  <si>
+    <t>SUBSCRIPTION PLANS</t>
   </si>
   <si>
     <t>Feature</t>
   </si>
   <si>
-    <t>Same user, different tenants</t>
-  </si>
-  <si>
-    <t>john can be admin at KINTO and viewer at ABC Mfg — different roles per tenant</t>
-  </si>
-  <si>
-    <t>Company switcher</t>
-  </si>
-  <si>
-    <t>Header shows company name with dropdown to switch tenant (no re-login needed)</t>
-  </si>
-  <si>
-    <t>Session update on switch</t>
-  </si>
-  <si>
-    <t>tenantId, role, planFlags updated in session when user switches company</t>
-  </si>
-  <si>
-    <t>isSuperAdmin=true flag — bypasses all tenant filters, sees all data</t>
-  </si>
-  <si>
-    <t>LICENSING &amp; PLAN STRUCTURE</t>
-  </si>
-  <si>
-    <t>Subscription Tiers  |  Enforcement Points  |  Grace Period Policy</t>
-  </si>
-  <si>
-    <t>SUBSCRIPTION PLANS</t>
-  </si>
-  <si>
     <t>Starter</t>
   </si>
   <si>
@@ -506,7 +478,7 @@
     <t>Unlimited</t>
   </si>
   <si>
-    <t>Extra user: ₹199/user/mo (Starter), ₹149 (Pro)</t>
+    <t>Extra user: ₹199/mo (Starter), ₹149 (Pro)</t>
   </si>
   <si>
     <t>File Storage</t>
@@ -518,7 +490,7 @@
     <t>25 GB</t>
   </si>
   <si>
-    <t>Enforced at upload time</t>
+    <t>Enforced at upload</t>
   </si>
   <si>
     <t>Invoicing &amp; GST</t>
@@ -527,16 +499,13 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>Core module — always included</t>
+    <t>Always included</t>
   </si>
   <si>
     <t>Accounting / Ledger</t>
   </si>
   <si>
-    <t>Sales Orders</t>
-  </si>
-  <si>
-    <t>Purchase Orders</t>
+    <t>Sales / Purchase Orders</t>
   </si>
   <si>
     <t>WhatsApp Integration</t>
@@ -545,37 +514,31 @@
     <t>No</t>
   </si>
   <si>
-    <t>Checklist reminders via WhatsApp</t>
+    <t>Checklist reminders</t>
   </si>
   <si>
     <t>BOM / Production</t>
   </si>
   <si>
-    <t>Bill of Materials, production tracking</t>
+    <t>Bill of Materials, tracking</t>
   </si>
   <si>
     <t>MIS Analytics</t>
   </si>
   <si>
-    <t>Executive dashboard, KPI reports</t>
+    <t>Executive KPI dashboard</t>
   </si>
   <si>
     <t>Document Management</t>
   </si>
   <si>
-    <t>Contracts, certificates, expiry alerts</t>
+    <t>Contracts, expiry alerts</t>
   </si>
   <si>
     <t>API Access</t>
   </si>
   <si>
-    <t>REST API for external integrations</t>
-  </si>
-  <si>
-    <t>Custom Domain</t>
-  </si>
-  <si>
-    <t>company.kintoops.com</t>
+    <t>REST API for integrations</t>
   </si>
   <si>
     <t>Priority Support</t>
@@ -599,61 +562,7 @@
     <t>30 days</t>
   </si>
   <si>
-    <t>Full Professional access during trial</t>
-  </si>
-  <si>
-    <t>ENFORCEMENT POINTS</t>
-  </si>
-  <si>
-    <t>Limit</t>
-  </si>
-  <si>
-    <t>Where Enforced</t>
-  </si>
-  <si>
-    <t>What Happens to User</t>
-  </si>
-  <si>
-    <t>User limit exceeded</t>
-  </si>
-  <si>
-    <t>400 error: "User limit reached. Upgrade your plan."</t>
-  </si>
-  <si>
-    <t>Module not in plan</t>
-  </si>
-  <si>
-    <t>403 error: "This feature requires Professional plan or above."</t>
-  </si>
-  <si>
-    <t>Storage quota reached</t>
-  </si>
-  <si>
-    <t>400 error: "Storage limit reached. Please upgrade."</t>
-  </si>
-  <si>
-    <t>Subscription expired</t>
-  </si>
-  <si>
-    <t>402 error: "Subscription expired. Please renew to continue."</t>
-  </si>
-  <si>
-    <t>In grace period (Day 1-7)</t>
-  </si>
-  <si>
-    <t>Read-only mode: can view, cannot create/edit/delete</t>
-  </si>
-  <si>
-    <t>Trial ended</t>
-  </si>
-  <si>
-    <t>402 error: "Trial ended. Please choose a plan to continue."</t>
-  </si>
-  <si>
-    <t>Account suspended</t>
-  </si>
-  <si>
-    <t>Login blocked. Data preserved. Contact admin to reactivate.</t>
+    <t>Full Pro access during trial</t>
   </si>
   <si>
     <t>GRACE PERIOD POLICY</t>
@@ -665,49 +574,43 @@
     <t>Event</t>
   </si>
   <si>
-    <t>Action / User Impact</t>
+    <t>Impact</t>
   </si>
   <si>
     <t>Day 0</t>
   </si>
   <si>
-    <t>Grace period begins. Read-only mode.</t>
+    <t>Grace starts. Read-only mode.</t>
   </si>
   <si>
     <t>Day 1–7</t>
   </si>
   <si>
-    <t>User can view all data but cannot create new records. Reminder emails sent.</t>
+    <t>Can view, cannot create/edit. Reminder emails sent.</t>
   </si>
   <si>
     <t>Day 8</t>
   </si>
   <si>
-    <t>Account suspended. Login blocked. Data fully preserved.</t>
-  </si>
-  <si>
-    <t>Day 8–90</t>
-  </si>
-  <si>
-    <t>Data retained. Reactivate anytime by renewing subscription.</t>
+    <t>Login blocked. Data preserved.</t>
   </si>
   <si>
     <t>Day 91</t>
   </si>
   <si>
-    <t>Email sent: "Your data will be deleted in 30 days."</t>
+    <t>Email: data deleted in 30 days.</t>
   </si>
   <si>
     <t>Day 120</t>
   </si>
   <si>
-    <t>All tenant data permanently deleted from database and file storage.</t>
+    <t>All data permanently removed.</t>
   </si>
   <si>
     <t>IMPLEMENTATION PHASES</t>
   </si>
   <si>
-    <t>Phased Build Plan  |  Scope  |  Effort  |  Timeline</t>
+    <t>11 Phases  |  ~36 Working Days  |  ~7–8 Weeks</t>
   </si>
   <si>
     <t>Phase</t>
@@ -716,7 +619,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Scope / Key Work Items</t>
+    <t>Scope</t>
   </si>
   <si>
     <t>Days</t>
@@ -734,7 +637,7 @@
     <t>DB Foundation</t>
   </si>
   <si>
-    <t>New tables (tenants, subscriptions, plans, billing). Add tenant_id to all 39 existing tables with DEFAULT 1. Insert default tenant (KINTO). Link all existing users to tenant 1.</t>
+    <t>New tables. Add tenant_id to all 39 tables with DEFAULT 1. Insert default tenant. Link existing users.</t>
   </si>
   <si>
     <t>Critical</t>
@@ -746,19 +649,19 @@
     <t>Auth &amp; Session</t>
   </si>
   <si>
-    <t>Two-step login flow. Tenant resolution on login. tenantId stored in session. Company switcher in header. Super admin flag.</t>
+    <t>Two-step login. Tenant resolution. Company switcher. Super admin flag.</t>
   </si>
   <si>
     <t>API Middleware</t>
   </si>
   <si>
-    <t>Tenant injection middleware. All 200+ routes auto-filtered by tenantId. Subscription check. Module gate. Super admin bypass.</t>
+    <t>Tenant injection on all 200+ routes. Subscription check. Module gate.</t>
   </si>
   <si>
     <t>File Upload Scoping</t>
   </si>
   <si>
-    <t>Restructure /uploads/{tenantId}/ folders. Migrate existing files to /uploads/1/. All upload routes prefix with tenantId. Storage quota check.</t>
+    <t>Tenant folders /uploads/{id}/. Migrate existing files. Storage quota.</t>
   </si>
   <si>
     <t>High</t>
@@ -767,73 +670,55 @@
     <t>License Engine</t>
   </si>
   <si>
-    <t>Plans table seeded. User limit enforcement on user create. Module access flags checked in middleware. Storage quota enforced at upload.</t>
+    <t>Plan seeding. User limit at creation. Module flags. Storage enforcement.</t>
   </si>
   <si>
     <t>Tenant Admin Portal</t>
   </si>
   <si>
-    <t>Settings section for tenant admin: company profile, logo upload, user management, subscription view, billing invoices.</t>
+    <t>Company profile, logo, user management, subscription view, billing.</t>
   </si>
   <si>
     <t>Super Admin Panel</t>
   </si>
   <si>
-    <t>All tenants list, create/suspend/reactivate, plan override, impersonation (audit-logged), billing overview, MRR dashboard.</t>
+    <t>All tenants, CRUD, plan override, impersonation, MRR dashboard.</t>
   </si>
   <si>
     <t>Billing Engine</t>
   </si>
   <si>
-    <t>Razorpay integration. Monthly auto-invoice generation (cron). Payment webhook. Receipt emails. Failed payment reminders. Grace period cron.</t>
+    <t>Razorpay. Auto-invoicing cron. Payment webhook. Receipts. Grace period.</t>
   </si>
   <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>WhatsApp &amp; Email per Tenant</t>
-  </si>
-  <si>
-    <t>Per-tenant WhatsApp credentials in settings. Webhook routes by phone_number_id to correct tenant. Branded emails (company name, logo, reply-to).</t>
+    <t>WhatsApp &amp; Email</t>
+  </si>
+  <si>
+    <t>Per-tenant credentials. Webhook routing. Branded emails.</t>
   </si>
   <si>
     <t>Reports &amp; Exports</t>
   </si>
   <si>
-    <t>Tenant company name + logo + GSTIN in all Excel/PDF exports. Super admin cross-tenant reports (MRR, usage, expiring).</t>
+    <t>Tenant branding in all exports. Super admin cross-tenant reports.</t>
   </si>
   <si>
     <t>Testing &amp; Hardening</t>
   </si>
   <si>
-    <t>Cross-tenant data leak tests. Module enforcement tests. Billing flow tests. Load testing. Security audit. UAT with KINTO.</t>
-  </si>
-  <si>
-    <t>TOTAL ESTIMATED EFFORT: ~33–36 working days  |  ~7–8 weeks</t>
-  </si>
-  <si>
-    <t>WHAT STAYS EXACTLY THE SAME (ZERO CHANGES)</t>
-  </si>
-  <si>
-    <t>All existing features: invoices, BOM, production, MIS, accounting, gatepasses, sales orders, purchase orders, checklists, documents, expenses</t>
-  </si>
-  <si>
-    <t>All existing user credentials and passwords — users log in exactly the same way</t>
-  </si>
-  <si>
-    <t>All existing data — auto-assigned to Tenant 1 with zero manual work</t>
-  </si>
-  <si>
-    <t>The entire UI, navigation, and page structure</t>
-  </si>
-  <si>
-    <t>All existing reports, Excel exports, and print layouts (tenant branding is additive, not replacing)</t>
+    <t>Cross-tenant leak tests. Module tests. Security audit. UAT.</t>
+  </si>
+  <si>
+    <t>TOTAL: ~33–36 working days  |  ~7–8 weeks</t>
   </si>
   <si>
     <t>SAAS PRODUCT &amp; DEPLOYMENT</t>
   </si>
   <si>
-    <t>Publishing on Replit  |  Cloud Options  |  SaaS Business Model</t>
+    <t>Replit Publishing  |  Cloud Options  |  Business Model</t>
   </si>
   <si>
     <t>DEPLOYMENT STAGES</t>
@@ -848,16 +733,16 @@
     <t>Why</t>
   </si>
   <si>
-    <t>Monthly Cost (est.)</t>
-  </si>
-  <si>
-    <t>Launch → First 50 tenants</t>
+    <t>Est. Monthly Cost</t>
+  </si>
+  <si>
+    <t>Launch → 50 tenants</t>
   </si>
   <si>
     <t>Replit Deployments</t>
   </si>
   <si>
-    <t>Zero DevOps. Click Publish. Auto-SSL. Custom domain. Focus on product not infrastructure.</t>
+    <t>Zero DevOps. Click Publish. Auto-SSL. Custom domain.</t>
   </si>
   <si>
     <t>₹2,000–4,000/mo</t>
@@ -866,10 +751,10 @@
     <t>50–500 tenants</t>
   </si>
   <si>
-    <t>AWS EC2 + RDS (Mumbai region)</t>
-  </si>
-  <si>
-    <t>More control. Indian data residency. Cost-effective at scale.</t>
+    <t>AWS EC2 + RDS Mumbai</t>
+  </si>
+  <si>
+    <t>Indian data residency. More control at scale.</t>
   </si>
   <si>
     <t>₹8,000–20,000/mo</t>
@@ -878,34 +763,10 @@
     <t>500+ tenants</t>
   </si>
   <si>
-    <t>AWS/GCP with Docker + Kubernetes</t>
-  </si>
-  <si>
-    <t>Full scalability. Load balancing. Auto-scaling. Multi-region.</t>
-  </si>
-  <si>
-    <t>WHAT REPLIT DEPLOYMENT GIVES YOU</t>
-  </si>
-  <si>
-    <t>yourapp.replit.app — accessible anywhere in the world instantly</t>
-  </si>
-  <si>
-    <t>Point kintoops.com or app.kintoops.com to your deployment</t>
-  </si>
-  <si>
-    <t>Included, no setup, auto-renews</t>
-  </si>
-  <si>
-    <t>Runs even when browser is closed</t>
-  </si>
-  <si>
-    <t>Zero downtime from application errors</t>
-  </si>
-  <si>
-    <t>All API keys (Razorpay, WhatsApp, SendGrid) stay secure</t>
-  </si>
-  <si>
-    <t>No EC2, no Docker, no Linux, no DevOps needed</t>
+    <t>AWS/GCP + Kubernetes</t>
+  </si>
+  <si>
+    <t>Full auto-scaling. Multi-region.</t>
   </si>
   <si>
     <t>SAAS BUSINESS MODEL</t>
@@ -914,37 +775,31 @@
     <t>Item</t>
   </si>
   <si>
-    <t>= SaaS Vendor. Your company uses the system for free as Tenant 1.</t>
-  </si>
-  <si>
-    <t>= Manufacturing companies paying monthly subscriptions.</t>
+    <t>SaaS Vendor. Your company uses the system for free as Tenant 1.</t>
+  </si>
+  <si>
+    <t>Manufacturing companies paying monthly subscriptions.</t>
   </si>
   <si>
     <t>MRR (Monthly Recurring Revenue) from all active tenants.</t>
   </si>
   <si>
-    <t>Customers sign up, complete wizard, start 14-day trial, choose plan, pay via Razorpay.</t>
+    <t>Signup → wizard → 14-day trial → choose plan → pay via Razorpay.</t>
   </si>
   <si>
     <t>Starter → Professional → Enterprise as companies grow.</t>
   </si>
   <si>
-    <t>Razorpay supports UPI, NEFT, credit/debit cards — best for Indian B2B.</t>
-  </si>
-  <si>
-    <t>Offer 2 months free on annual plan to encourage commitment.</t>
-  </si>
-  <si>
-    <t>50 tenants or 500 tenants — same codebase, same Replit deployment until you need more.</t>
+    <t>2 months free on annual upfront payment.</t>
   </si>
   <si>
     <t>INTEGRATIONS &amp; SERVICES IMPACT</t>
   </si>
   <si>
-    <t>WhatsApp  |  Email  |  Files  |  Reports  |  API</t>
-  </si>
-  <si>
-    <t>WHATSAPP INTEGRATION</t>
+    <t>WhatsApp  |  Email  |  Files  |  Reports</t>
+  </si>
+  <si>
+    <t>WHATSAPP</t>
   </si>
   <si>
     <t>Aspect</t>
@@ -968,43 +823,34 @@
     <t>Outgoing reminders</t>
   </si>
   <si>
-    <t>Checklist completion</t>
-  </si>
-  <si>
-    <t>EMAIL NOTIFICATIONS</t>
+    <t>EMAIL</t>
   </si>
   <si>
     <t>Setting</t>
   </si>
   <si>
+    <t>After</t>
+  </si>
+  <si>
     <t>Sender name</t>
   </si>
   <si>
     <t>Reply-to</t>
   </si>
   <si>
-    <t>Email logo</t>
-  </si>
-  <si>
     <t>Machine reminders</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>Document expiry alerts</t>
-  </si>
-  <si>
-    <t>Subscription reminders</t>
-  </si>
-  <si>
-    <t>FILE UPLOADS &amp; DOCUMENTS</t>
-  </si>
-  <si>
-    <t>Folder structure</t>
-  </si>
-  <si>
-    <t>Access control</t>
+    <t>Subscription alerts</t>
+  </si>
+  <si>
+    <t>FILE UPLOADS</t>
+  </si>
+  <si>
+    <t>Folder</t>
   </si>
   <si>
     <t>Existing files</t>
@@ -1013,10 +859,10 @@
     <t>Storage quota</t>
   </si>
   <si>
-    <t>Cross-tenant access</t>
-  </si>
-  <si>
-    <t>REPORTS &amp; EXCEL EXPORTS</t>
+    <t>Cross-access</t>
+  </si>
+  <si>
+    <t>REPORTS &amp; EXPORTS</t>
   </si>
   <si>
     <t>Report</t>
@@ -1025,34 +871,28 @@
     <t>Change</t>
   </si>
   <si>
-    <t>All operational reports</t>
+    <t>All reports</t>
   </si>
   <si>
     <t>Excel exports</t>
   </si>
   <si>
-    <t>PDF invoices / gatepasses</t>
-  </si>
-  <si>
-    <t>MIS Dashboard</t>
-  </si>
-  <si>
-    <t>Trial Balance / P&amp;L / Balance Sheet</t>
-  </si>
-  <si>
-    <t>Super Admin MRR report</t>
+    <t>PDF invoices</t>
+  </si>
+  <si>
+    <t>Super Admin MRR</t>
   </si>
   <si>
     <t>CUSTOMIZATION PRICING</t>
   </si>
   <si>
-    <t>Fixed Price Model  |  One Clear Rate  |  No Hourly Billing</t>
+    <t>Fixed Price Only  |  Quote Upfront  |  No Hourly Billing</t>
   </si>
   <si>
     <t>RULE: All customizations are Fixed Price only. Quote upfront. Customer approves before work starts. No hourly billing. No ambiguity.</t>
   </si>
   <si>
-    <t>CUSTOMIZATION PRICE LIST</t>
+    <t>PRICE LIST</t>
   </si>
   <si>
     <t>Customization Type</t>
@@ -1076,7 +916,7 @@
     <t>₹15,000</t>
   </si>
   <si>
-    <t>New Excel or PDF report specific to one customer — layout, data, columns as per their requirement</t>
+    <t>New Excel/PDF report — layout, data, columns as per requirement</t>
   </si>
   <si>
     <t>Custom Fields in a Module</t>
@@ -1088,7 +928,7 @@
     <t>₹8,000</t>
   </si>
   <si>
-    <t>Additional fields not in standard forms — invoices, production, checklist, etc.</t>
+    <t>Additional fields not in standard forms</t>
   </si>
   <si>
     <t>Custom Workflow / Approval Flow</t>
@@ -1100,7 +940,7 @@
     <t>₹30,000</t>
   </si>
   <si>
-    <t>Different approval stages, state changes, rules or conditions specific to one customer</t>
+    <t>Different approval stages, state changes, rules for one customer</t>
   </si>
   <si>
     <t>API / Tally / ERP Integration</t>
@@ -1109,7 +949,7 @@
     <t>₹50,000</t>
   </si>
   <si>
-    <t>Connect Kinto with customer's existing Tally, ERP, or third-party software via API</t>
+    <t>Connect Kinto with existing Tally, ERP or third-party software</t>
   </si>
   <si>
     <t>WhatsApp Custom Flow</t>
@@ -1118,7 +958,7 @@
     <t>₹20,000</t>
   </si>
   <si>
-    <t>Custom bot messages, custom checklist templates, custom reminder logic for WhatsApp</t>
+    <t>Custom bot messages, checklist templates, reminder logic</t>
   </si>
   <si>
     <t>Custom MIS Dashboard</t>
@@ -1127,22 +967,22 @@
     <t>₹25,000</t>
   </si>
   <si>
-    <t>New MIS widgets, KPIs, charts or analytics screens specific to customer's operations</t>
-  </si>
-  <si>
-    <t>Data Migration (Historical Import)</t>
-  </si>
-  <si>
-    <t>Import customer's historical data from Excel, Tally, or other software into Kinto</t>
+    <t>New KPI widgets, charts or analytics screens</t>
+  </si>
+  <si>
+    <t>Data Migration</t>
+  </si>
+  <si>
+    <t>Import historical data from Excel, Tally or other software</t>
   </si>
   <si>
     <t>Training Session</t>
   </si>
   <si>
-    <t>Per session — on-site or remote training for customer's team (per session rate)</t>
-  </si>
-  <si>
-    <t>Priority Support SLA (Monthly)</t>
+    <t>Per session — on-site or remote. Per session rate.</t>
+  </si>
+  <si>
+    <t>Priority SLA (Monthly Add-on)</t>
   </si>
   <si>
     <t>₹2,000/mo</t>
@@ -1151,16 +991,16 @@
     <t>₹5,000/mo</t>
   </si>
   <si>
-    <t>Guaranteed response time add-on (e.g. 4-hour response). Billed monthly on top of subscription.</t>
-  </si>
-  <si>
-    <t>THE PROCESS — HOW EVERY CUSTOMIZATION WORKS</t>
+    <t>Guaranteed response time. Billed monthly on top of subscription.</t>
+  </si>
+  <si>
+    <t>THE PROCESS</t>
   </si>
   <si>
     <t>Action</t>
   </si>
   <si>
-    <t>Who Does It</t>
+    <t>Who</t>
   </si>
   <si>
     <t>Customer</t>
@@ -1190,35 +1030,624 @@
     <t>7</t>
   </si>
   <si>
-    <t>WHAT IS INCLUDED IN SUBSCRIPTION (NO EXTRA CHARGE)</t>
-  </si>
-  <si>
-    <t>Standard features available to all tenants on their plan</t>
-  </si>
-  <si>
-    <t>Bug fixes and error corrections in existing functionality</t>
-  </si>
-  <si>
-    <t>New platform features released by Kinto to all tenants (everyone gets them automatically)</t>
-  </si>
-  <si>
-    <t>Configuration within the app — roles, permissions, categories, expense types, chart of accounts, etc.</t>
-  </si>
-  <si>
-    <t>Email and WhatsApp support for how-to questions within standard usage</t>
-  </si>
-  <si>
-    <t>KEY RULE: STANDARD vs CUSTOM</t>
-  </si>
-  <si>
-    <t>If a customization built for one customer is useful to all customers → add it to the standard platform (free for everyone, grows the product). If it is specific only to that one customer → charge separately and maintain it as their private feature.</t>
+    <t>PITCH DECK — SLIDE-BY-SLIDE OUTLINE</t>
+  </si>
+  <si>
+    <t>Investor / Customer Presentation  |  12 Slides</t>
+  </si>
+  <si>
+    <t>12-SLIDE PITCH DECK OUTLINE</t>
+  </si>
+  <si>
+    <t>Use this as script for PowerPoint / Google Slides / Canva. Each slide = one focused message.</t>
+  </si>
+  <si>
+    <t>Slide</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Content / Key Points</t>
+  </si>
+  <si>
+    <t>Speaker Notes / Design Tip</t>
+  </si>
+  <si>
+    <t>Cover Slide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinto Smart Ops
+The Operating System for Indian Manufacturing
+[Logo] | [Tagline] | [Contact]</t>
+  </si>
+  <si>
+    <t>Keep it clean. One line tagline. Company logo prominent.</t>
+  </si>
+  <si>
+    <t>The Problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indian manufacturing SMEs run on WhatsApp messages, Excel sheets, and paper registers.
+→ No real-time visibility
+→ GST compliance errors
+→ Inventory goes missing
+→ Quality issues not tracked
+→ Production is guesswork</t>
+  </si>
+  <si>
+    <t>Use real pain points. Show a chaotic WhatsApp screenshot or messy spreadsheet as visual.</t>
+  </si>
+  <si>
+    <t>The Solution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kinto Smart Ops — One platform for:
+✔ Invoicing &amp; GST
+✔ Inventory &amp; Production
+✔ Quality &amp; Checklists
+✔ WhatsApp-based operator tasks
+✔ Financial accounting
+✔ MIS analytics for management</t>
+  </si>
+  <si>
+    <t>Screenshot of the actual dashboard. Show it is already built — not a concept.</t>
+  </si>
+  <si>
+    <t>Product Demo Snapshot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Show 4–5 key screens:
+1. Dashboard / MIS overview
+2. Invoice creation with GST
+3. WhatsApp checklist interaction
+4. Production BOM tracking
+5. Pending payments tracker</t>
+  </si>
+  <si>
+    <t>Real product screenshots. No mockups. This is your strongest slide.</t>
+  </si>
+  <si>
+    <t>Market Opportunity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">India has 63 million MSMEs
+→ 3.5 million in manufacturing
+→ &lt;5% use dedicated ERP software
+→ Most use Tally (accounting only) + paper for operations
+Addrессable market: ₹8,000+ crore/year
+Target: Tier 2 / Tier 3 manufacturing cities</t>
+  </si>
+  <si>
+    <t>Cite MSME Ministry data. Focus on underserved segment — not large enterprises already using SAP.</t>
+  </si>
+  <si>
+    <t>Business Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SaaS Subscription (recurring revenue)
+Starter:       ₹999/month  (3 users)
+Professional:  ₹2,499/month (10 users)
+Enterprise:    Custom pricing
++ Customization services (fixed price per project)
++ Annual plan: 2 months free
++ 14-day free trial — no credit card required</t>
+  </si>
+  <si>
+    <t>Emphasize MRR predictability. Show example: 100 Professional customers = ₹25 lakh/month.</t>
+  </si>
+  <si>
+    <t>Traction &amp; Proof</t>
+  </si>
+  <si>
+    <t xml:space="preserve">✔ Fully built and operational at KINTO (live production use)
+✔ [X] months of real operational data
+✔ Handles invoicing, BOM, production, accounting, dispatch
+✔ WhatsApp integration live with operators
+✔ Zero paper records since go-live</t>
+  </si>
+  <si>
+    <t>This is your unfair advantage — you built it for yourself first. It is proven, not theoretical.</t>
+  </si>
+  <si>
+    <t>Why Now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">→ GST e-invoicing mandates expanding to smaller businesses
+→ WhatsApp Business API now accessible to SMEs
+→ Post-COVID: factories want digital records for audits
+→ "Make in India" push increasing manufacturing activity
+→ Competitors are too expensive (SAP, Oracle) or too simple (Vyapaar, Zoho Books)</t>
+  </si>
+  <si>
+    <t>Regulatory tailwinds. Show the gap between ₹500/mo basic tools and ₹50,000/mo enterprise ERP.</t>
+  </si>
+  <si>
+    <t>Competition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zoho Books / Tally → Accounting only, no operations
+SAP / Oracle → ₹10L+ implementation, not for SMEs
+Odoo → Complex, needs IT team
+Vyapaar / Marg → Basic invoicing only
+Kinto: Operations + Quality + WhatsApp + Accounting
+All-in-one. Indian pricing. Built for shop-floor reality.</t>
+  </si>
+  <si>
+    <t>Position clearly. You are not trying to replace SAP. You are the alternative to Excel + WhatsApp chaos.</t>
+  </si>
+  <si>
+    <t>Go-To-Market Strategy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phase 1: Direct sales to 10 anchor customers (manufacturing contacts)
+Phase 2: Digital marketing — Google, LinkedIn, YouTube demos
+Phase 3: Channel partners — CA firms, equipment vendors, industry associations
+Phase 4: Self-service signup with free trial
+Target cities: Coimbatore, Pune, Ludhiana, Rajkot, Ahmedabad, Faridabad</t>
+  </si>
+  <si>
+    <t>Show you have a plan. Mention any warm leads or existing conversations.</t>
+  </si>
+  <si>
+    <t>Financial Projections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year 1:  25 customers  →  ₹7.5L ARR
+Year 2:  100 customers →  ₹30L ARR
+Year 3:  300 customers →  ₹90L ARR
++ Customization revenue: 20–30% on top
+Gross margin: 85%+ (SaaS model)
+Break-even: ~40 paying customers</t>
+  </si>
+  <si>
+    <t>Conservative, credible numbers. Do not over-project. Show path to profitability clearly.</t>
+  </si>
+  <si>
+    <t>The Ask / Next Steps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For Investors:
+→ Seed funding ask: ₹[X] crore
+→ Use of funds: Sales team, marketing, cloud infra
+→ Target: 100 paying customers in 12 months
+For Customers:
+→ Start free 14-day trial today
+→ No credit card. No lock-in.
+→ [Your contact] | [Demo link]</t>
+  </si>
+  <si>
+    <t>End with a clear call to action. For customer pitch — make it easy to say yes with a free trial.</t>
+  </si>
+  <si>
+    <t>DESIGN TIPS FOR THE DECK</t>
+  </si>
+  <si>
+    <t>Use Canva (free) or Google Slides. Choose a clean, professional dark template.</t>
+  </si>
+  <si>
+    <t>One idea per slide. Never put more than 5 bullet points on one slide.</t>
+  </si>
+  <si>
+    <t>Use real product screenshots — not mockups or illustrations.</t>
+  </si>
+  <si>
+    <t>Slides 2 (Problem) and 7 (Traction) are your most important. Spend most time on them.</t>
+  </si>
+  <si>
+    <t>Keep total deck to 12–15 slides. Investors read decks in under 3 minutes.</t>
+  </si>
+  <si>
+    <t>Have a 1-page PDF summary version for WhatsApp / email sharing.</t>
+  </si>
+  <si>
+    <t>DIGITAL MARKETING PLAN</t>
+  </si>
+  <si>
+    <t>Channels  |  Content Strategy  |  Budget  |  90-Day Calendar</t>
+  </si>
+  <si>
+    <t>TARGET AUDIENCE</t>
+  </si>
+  <si>
+    <t>Persona</t>
+  </si>
+  <si>
+    <t>Who They Are</t>
+  </si>
+  <si>
+    <t>Their Pain</t>
+  </si>
+  <si>
+    <t>Where to Find Them</t>
+  </si>
+  <si>
+    <t>Factory Owner / MD</t>
+  </si>
+  <si>
+    <t>Runs manufacturing unit, 10–100 employees. Wants visibility and control.</t>
+  </si>
+  <si>
+    <t>No real-time data. Relies on phone calls to know production status.</t>
+  </si>
+  <si>
+    <t>LinkedIn, Google Search, Industry WhatsApp groups</t>
+  </si>
+  <si>
+    <t>Production Manager</t>
+  </si>
+  <si>
+    <t>Manages daily output, BOM, quality. Drowning in paperwork.</t>
+  </si>
+  <si>
+    <t>Manual registers. Errors in material consumption. No BOM tracking.</t>
+  </si>
+  <si>
+    <t>LinkedIn, YouTube (process videos), Google</t>
+  </si>
+  <si>
+    <t>Accountant / Finance Head</t>
+  </si>
+  <si>
+    <t>Handles GST, invoicing, payments. Uses Tally.</t>
+  </si>
+  <si>
+    <t>Tally has no operations link. Manual invoice matching. GST errors.</t>
+  </si>
+  <si>
+    <t>Google Search ("GST software for manufacturers"), CA networks</t>
+  </si>
+  <si>
+    <t>Business Owner (SME)</t>
+  </si>
+  <si>
+    <t>Wants to grow but operations are chaotic.</t>
+  </si>
+  <si>
+    <t>Cannot delegate without visibility. Afraid of scale.</t>
+  </si>
+  <si>
+    <t>Facebook, LinkedIn, Google</t>
+  </si>
+  <si>
+    <t>MARKETING CHANNELS &amp; TACTICS</t>
+  </si>
+  <si>
+    <t>Channel</t>
+  </si>
+  <si>
+    <t>Tactic</t>
+  </si>
+  <si>
+    <t>Content / Format</t>
+  </si>
+  <si>
+    <t>Monthly Budget</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Google Search Ads</t>
+  </si>
+  <si>
+    <t>Bid on high-intent keywords</t>
+  </si>
+  <si>
+    <t>"Manufacturing ERP India", "GST invoicing software", "production tracking software"</t>
+  </si>
+  <si>
+    <t>₹8,000–15,000</t>
+  </si>
+  <si>
+    <t>Direct trial signups — highest intent leads</t>
+  </si>
+  <si>
+    <t>Google Display / YouTube</t>
+  </si>
+  <si>
+    <t>Product demo video ads</t>
+  </si>
+  <si>
+    <t>60-sec demo: "How KINTO replaced our paper registers" — real factory footage</t>
+  </si>
+  <si>
+    <t>₹5,000–10,000</t>
+  </si>
+  <si>
+    <t>Brand awareness in manufacturing sector</t>
+  </si>
+  <si>
+    <t>LinkedIn Ads</t>
+  </si>
+  <si>
+    <t>Target by job title + industry</t>
+  </si>
+  <si>
+    <t>Carousel: Before (Excel chaos) vs After (Kinto dashboard). Target: Production Mgr, Factory Owner</t>
+  </si>
+  <si>
+    <t>₹8,000–12,000</t>
+  </si>
+  <si>
+    <t>B2B decision-maker reach</t>
+  </si>
+  <si>
+    <t>LinkedIn Organic</t>
+  </si>
+  <si>
+    <t>Weekly content posts</t>
+  </si>
+  <si>
+    <t>Post 3x/week: tips, feature highlights, customer wins, factory operations content</t>
+  </si>
+  <si>
+    <t>₹0 (time only)</t>
+  </si>
+  <si>
+    <t>Thought leadership, inbound leads</t>
+  </si>
+  <si>
+    <t>YouTube Channel</t>
+  </si>
+  <si>
+    <t>Feature walkthrough videos</t>
+  </si>
+  <si>
+    <t>5–10 min demos: "How to create GST invoice", "BOM tracking demo", "WhatsApp checklist"</t>
+  </si>
+  <si>
+    <t>SEO + trust building. Long-term inbound.</t>
+  </si>
+  <si>
+    <t>WhatsApp Broadcast</t>
+  </si>
+  <si>
+    <t>Warm lead nurturing</t>
+  </si>
+  <si>
+    <t>Weekly tip + feature update to opted-in contacts. Use Kinto's own WhatsApp integration.</t>
+  </si>
+  <si>
+    <t>₹0</t>
+  </si>
+  <si>
+    <t>Re-engage trials, convert to paid</t>
+  </si>
+  <si>
+    <t>SEO / Blog</t>
+  </si>
+  <si>
+    <t>Rank for manufacturing ops keywords</t>
+  </si>
+  <si>
+    <t>Articles: "How to reduce material waste", "GST e-invoicing guide for manufacturers"</t>
+  </si>
+  <si>
+    <t>₹0 (or ₹3,000 writer)</t>
+  </si>
+  <si>
+    <t>Organic long-term traffic</t>
+  </si>
+  <si>
+    <t>Industry Associations</t>
+  </si>
+  <si>
+    <t>Speak at events, sponsor newsletters</t>
+  </si>
+  <si>
+    <t>CII, FICCI, MSME associations. Coimbatore, Pune, Ludhiana chapters.</t>
+  </si>
+  <si>
+    <t>₹5,000–20,000</t>
+  </si>
+  <si>
+    <t>Credibility + warm introductions</t>
+  </si>
+  <si>
+    <t>CA / Consultant Partners</t>
+  </si>
+  <si>
+    <t>Referral program</t>
+  </si>
+  <si>
+    <t>CA recommends Kinto to their manufacturing clients. 20% revenue share for 12 months.</t>
+  </si>
+  <si>
+    <t>₹0 (commission)</t>
+  </si>
+  <si>
+    <t>High-quality referrals from trusted advisors</t>
+  </si>
+  <si>
+    <t>Free Trial Landing Page</t>
+  </si>
+  <si>
+    <t>Conversion-optimised page</t>
+  </si>
+  <si>
+    <t>Headline: "Run your factory from one screen." CTA: "Start free 14-day trial — no card needed"</t>
+  </si>
+  <si>
+    <t>₹0 (one-time build)</t>
+  </si>
+  <si>
+    <t>All traffic converts here</t>
+  </si>
+  <si>
+    <t>CONTENT CALENDAR — FIRST 90 DAYS</t>
+  </si>
+  <si>
+    <t>Week</t>
+  </si>
+  <si>
+    <t>Focus</t>
+  </si>
+  <si>
+    <t>Content Pieces</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Week 1–2</t>
+  </si>
+  <si>
+    <t>Launch &amp; awareness</t>
+  </si>
+  <si>
+    <t>Product demo video (60 sec), LinkedIn announcement post, Google Ads live</t>
+  </si>
+  <si>
+    <t>YouTube, LinkedIn, Google</t>
+  </si>
+  <si>
+    <t>First 100 visitors to landing page</t>
+  </si>
+  <si>
+    <t>Week 3–4</t>
+  </si>
+  <si>
+    <t>Problem content</t>
+  </si>
+  <si>
+    <t>Blog: "5 signs your factory needs ERP", LinkedIn post: "What WhatsApp chaos costs you"</t>
+  </si>
+  <si>
+    <t>LinkedIn, Blog, WhatsApp</t>
+  </si>
+  <si>
+    <t>Build email list, 20+ trial signups</t>
+  </si>
+  <si>
+    <t>Week 5–6</t>
+  </si>
+  <si>
+    <t>Feature spotlight</t>
+  </si>
+  <si>
+    <t>Video: GST invoice demo, Post: BOM tracking walkthrough, Email to trial users</t>
+  </si>
+  <si>
+    <t>YouTube, LinkedIn, Email</t>
+  </si>
+  <si>
+    <t>Trial activation — get users to use key features</t>
+  </si>
+  <si>
+    <t>Week 7–8</t>
+  </si>
+  <si>
+    <t>Social proof</t>
+  </si>
+  <si>
+    <t>Customer story (with KINTO as Tenant 1), "Before vs After" LinkedIn carousel</t>
+  </si>
+  <si>
+    <t>LinkedIn, WhatsApp</t>
+  </si>
+  <si>
+    <t>Trust building, referral requests</t>
+  </si>
+  <si>
+    <t>Week 9–10</t>
+  </si>
+  <si>
+    <t>Competitor comparison</t>
+  </si>
+  <si>
+    <t>Blog: "Kinto vs Tally vs Zoho — which is right for manufacturers?"</t>
+  </si>
+  <si>
+    <t>Blog, Google</t>
+  </si>
+  <si>
+    <t>Capture comparison-stage buyers</t>
+  </si>
+  <si>
+    <t>Week 11–12</t>
+  </si>
+  <si>
+    <t>Conversion push</t>
+  </si>
+  <si>
+    <t>Free trial reminder emails, WhatsApp follow-up, Offer: 3 months free on annual</t>
+  </si>
+  <si>
+    <t>Email, WhatsApp, LinkedIn</t>
+  </si>
+  <si>
+    <t>Convert trials to paid subscriptions</t>
+  </si>
+  <si>
+    <t>MONTHLY MARKETING BUDGET (STARTER)</t>
+  </si>
+  <si>
+    <t>Focus on high-intent keywords only. Pause low-performers weekly.</t>
+  </si>
+  <si>
+    <t>Target Factory Owner + Production Manager job titles in manufacturing industry.</t>
+  </si>
+  <si>
+    <t>YouTube Ads</t>
+  </si>
+  <si>
+    <t>Promote demo video. Skip if organic YouTube getting views.</t>
+  </si>
+  <si>
+    <t>Content creation (if outsourced)</t>
+  </si>
+  <si>
+    <t>Blog articles + video editing. Can do in-house to save cost.</t>
+  </si>
+  <si>
+    <t>Industry events / associations</t>
+  </si>
+  <si>
+    <t>One event per month. Sponsor or speak.</t>
+  </si>
+  <si>
+    <t>Tools (email, analytics, CRM)</t>
+  </si>
+  <si>
+    <t>₹2,000</t>
+  </si>
+  <si>
+    <t>Mailchimp or Brevo for email. Google Analytics free.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>₹35,000/mo</t>
+  </si>
+  <si>
+    <t>Scale up as revenue grows. At 10 customers, reinvest 20% of MRR into marketing.</t>
+  </si>
+  <si>
+    <t>KEY MESSAGES (USE IN ALL CONTENT)</t>
+  </si>
+  <si>
+    <t>Run your entire factory from one screen.</t>
+  </si>
+  <si>
+    <t>Stop managing your factory on WhatsApp and Excel.</t>
+  </si>
+  <si>
+    <t>Built by manufacturers, for manufacturers. Running live in a real factory.</t>
+  </si>
+  <si>
+    <t>The only platform that connects your shop floor, accounts, and management — in one tool.</t>
+  </si>
+  <si>
+    <t>Start your free 14-day trial. No credit card. No lock-in.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1291,23 +1720,18 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF1E293B"/>
+      <color rgb="FF14532D"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF14532D"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF78350F"/>
+      <color rgb="FF1E293B"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1369,8 +1793,18 @@
         <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDE9FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE7F3"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1409,11 +1843,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color rgb="FFE2E8F0"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFE2E8F0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1519,17 +1964,44 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2160,6 +2632,759 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G47"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="6" width="15" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>398</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>399</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>408</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>409</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+    </row>
+    <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+    </row>
+    <row r="11" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>418</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>421</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>422</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>424</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>431</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>432</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>433</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>434</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>435</v>
+      </c>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+    </row>
+    <row r="16" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>438</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>440</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>441</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+    </row>
+    <row r="18" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>449</v>
+      </c>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>450</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>451</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>452</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>453</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>454</v>
+      </c>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>460</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>461</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>463</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="F21" s="8"/>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
+    </row>
+    <row r="25" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="47" t="s">
+        <v>475</v>
+      </c>
+      <c r="B26" s="47" t="s">
+        <v>476</v>
+      </c>
+      <c r="C26" s="47" t="s">
+        <v>477</v>
+      </c>
+      <c r="D26" s="47" t="s">
+        <v>478</v>
+      </c>
+      <c r="E26" s="47" t="s">
+        <v>479</v>
+      </c>
+      <c r="F26" s="47"/>
+      <c r="G26" s="47"/>
+    </row>
+    <row r="27" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="47" t="s">
+        <v>485</v>
+      </c>
+      <c r="B28" s="47" t="s">
+        <v>486</v>
+      </c>
+      <c r="C28" s="47" t="s">
+        <v>487</v>
+      </c>
+      <c r="D28" s="47" t="s">
+        <v>488</v>
+      </c>
+      <c r="E28" s="47" t="s">
+        <v>489</v>
+      </c>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+    </row>
+    <row r="29" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="47" t="s">
+        <v>495</v>
+      </c>
+      <c r="B30" s="47" t="s">
+        <v>496</v>
+      </c>
+      <c r="C30" s="47" t="s">
+        <v>497</v>
+      </c>
+      <c r="D30" s="47" t="s">
+        <v>498</v>
+      </c>
+      <c r="E30" s="47" t="s">
+        <v>499</v>
+      </c>
+      <c r="F30" s="47"/>
+      <c r="G30" s="47"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>502</v>
+      </c>
+      <c r="D35" s="8"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="D37" s="8"/>
+      <c r="E37" s="8"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8"/>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>508</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="48" t="s">
+        <v>512</v>
+      </c>
+      <c r="B40" s="48" t="s">
+        <v>513</v>
+      </c>
+      <c r="C40" s="48" t="s">
+        <v>514</v>
+      </c>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+    </row>
+    <row r="42" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="3"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3"/>
+    </row>
+    <row r="43" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="49" t="s">
+        <v>516</v>
+      </c>
+      <c r="C43" s="49"/>
+      <c r="D43" s="49"/>
+      <c r="E43" s="49"/>
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+    </row>
+    <row r="44" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="47"/>
+      <c r="F44" s="47"/>
+      <c r="G44" s="47"/>
+    </row>
+    <row r="45" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="47" t="s">
+        <v>519</v>
+      </c>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="47"/>
+      <c r="F46" s="47"/>
+      <c r="G46" s="47"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="43">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="D4:G4"/>
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="E11:G11"/>
+    <mergeCell ref="E12:G12"/>
+    <mergeCell ref="E13:G13"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="E15:G15"/>
+    <mergeCell ref="E16:G16"/>
+    <mergeCell ref="E17:G17"/>
+    <mergeCell ref="E18:G18"/>
+    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="E20:G20"/>
+    <mergeCell ref="E21:G21"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="E24:G24"/>
+    <mergeCell ref="E25:G25"/>
+    <mergeCell ref="E26:G26"/>
+    <mergeCell ref="E27:G27"/>
+    <mergeCell ref="E28:G28"/>
+    <mergeCell ref="E29:G29"/>
+    <mergeCell ref="E30:G30"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="C38:G38"/>
+    <mergeCell ref="C39:G39"/>
+    <mergeCell ref="C40:G40"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="B43:G43"/>
+    <mergeCell ref="B44:G44"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B47:G47"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G30"/>
@@ -2662,7 +3887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -2974,111 +4199,8 @@
       <c r="F21" s="8"/>
       <c r="G21" s="8"/>
     </row>
-    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-    </row>
-    <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-    </row>
   </sheetData>
-  <mergeCells count="27">
+  <mergeCells count="20">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -3099,13 +4221,6 @@
     <mergeCell ref="D19:G19"/>
     <mergeCell ref="D20:G20"/>
     <mergeCell ref="D21:G21"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3114,7 +4229,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -3124,7 +4239,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3135,7 +4250,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3146,7 +4261,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -3160,554 +4275,370 @@
         <v>138</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="F5" s="17"/>
       <c r="G5" s="17"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="16" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="16" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F11" s="17"/>
       <c r="G11" s="17"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D12" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="16" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C13" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E13" s="17" t="s">
         <v>168</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>177</v>
       </c>
       <c r="F13" s="17"/>
       <c r="G13" s="17"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="D14" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="16" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="F15" s="17"/>
       <c r="G15" s="17"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="20" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B16" s="17" t="s">
         <v>174</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>183</v>
+        <v>91</v>
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="B17" s="17" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="E17" s="17" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="F17" s="17"/>
       <c r="G17" s="17"/>
     </row>
-    <row r="18" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
+    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C21" s="22" t="s">
         <v>186</v>
       </c>
-      <c r="B18" s="17" t="s">
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="B22" s="22" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B23" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="C23" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="B19" s="17" t="s">
+      <c r="B24" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="C19" s="18" t="s">
-        <v>191</v>
-      </c>
-      <c r="D19" s="19" t="s">
+      <c r="C24" s="24" t="s">
         <v>192</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B25" s="24" t="s">
         <v>193</v>
       </c>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="C25" s="24" t="s">
         <v>194</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>202</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>204</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>209</v>
-      </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>216</v>
-      </c>
-      <c r="C33" s="22" t="s">
-        <v>217</v>
-      </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="22" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C34" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B35" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="F35" s="23"/>
-      <c r="G35" s="23"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
-        <v>91</v>
-      </c>
-      <c r="B36" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="D36" s="23"/>
-      <c r="E36" s="23"/>
-      <c r="F36" s="23"/>
-      <c r="G36" s="23"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B37" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D37" s="24"/>
-      <c r="E37" s="24"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="24"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B38" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="C38" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="36">
+  <mergeCells count="24">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -3725,25 +4656,13 @@
     <mergeCell ref="E15:G15"/>
     <mergeCell ref="E16:G16"/>
     <mergeCell ref="E17:G17"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="E19:G19"/>
-    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="C26:G26"/>
-    <mergeCell ref="C27:G27"/>
-    <mergeCell ref="C28:G28"/>
-    <mergeCell ref="C29:G29"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="C38:G38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3752,7 +4671,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3765,7 +4684,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>228</v>
+        <v>195</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3776,7 +4695,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>229</v>
+        <v>196</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3787,36 +4706,36 @@
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>230</v>
+        <v>197</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>232</v>
+        <v>199</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>233</v>
+        <v>200</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>234</v>
+        <v>201</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>235</v>
+        <v>202</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="25">
         <v>1</v>
       </c>
       <c r="B4" s="26" t="s">
-        <v>237</v>
+        <v>204</v>
       </c>
       <c r="C4" s="27" t="s">
-        <v>238</v>
+        <v>205</v>
       </c>
       <c r="D4" s="28">
         <v>3</v>
@@ -3825,21 +4744,21 @@
         <v>3</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="5" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="29">
         <v>2</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>241</v>
+        <v>208</v>
       </c>
       <c r="C5" s="31" t="s">
-        <v>242</v>
+        <v>209</v>
       </c>
       <c r="D5" s="28">
         <v>3</v>
@@ -3848,21 +4767,21 @@
         <v>6</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="25">
         <v>3</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>243</v>
+        <v>210</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>244</v>
+        <v>211</v>
       </c>
       <c r="D6" s="28">
         <v>4</v>
@@ -3871,21 +4790,21 @@
         <v>10</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="29">
         <v>4</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>245</v>
+        <v>212</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>246</v>
+        <v>213</v>
       </c>
       <c r="D7" s="32">
         <v>2</v>
@@ -3894,21 +4813,21 @@
         <v>12</v>
       </c>
       <c r="F7" s="31" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="G7" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="25">
         <v>5</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>248</v>
+        <v>215</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="D8" s="32">
         <v>3</v>
@@ -3917,21 +4836,21 @@
         <v>15</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="9" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="29">
         <v>6</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D9" s="33">
         <v>4</v>
@@ -3940,21 +4859,21 @@
         <v>19</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="G9" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="10" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="25">
         <v>7</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="D10" s="33">
         <v>4</v>
@@ -3963,21 +4882,21 @@
         <v>23</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>247</v>
+        <v>214</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="11" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="29">
         <v>8</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>255</v>
+        <v>222</v>
       </c>
       <c r="D11" s="34">
         <v>5</v>
@@ -3986,21 +4905,21 @@
         <v>28</v>
       </c>
       <c r="F11" s="31" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="G11" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="12" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="12" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="25">
         <v>9</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>257</v>
+        <v>224</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>258</v>
+        <v>225</v>
       </c>
       <c r="D12" s="34">
         <v>3</v>
@@ -4009,21 +4928,21 @@
         <v>31</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="13" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="13" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="29">
         <v>10</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>260</v>
+        <v>227</v>
       </c>
       <c r="D13" s="35">
         <v>2</v>
@@ -4032,21 +4951,21 @@
         <v>33</v>
       </c>
       <c r="F13" s="31" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="G13" s="31" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="14" ht="38" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" ht="34" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="25">
         <v>11</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>261</v>
+        <v>228</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>262</v>
+        <v>229</v>
       </c>
       <c r="D14" s="32">
         <v>3</v>
@@ -4055,15 +4974,15 @@
         <v>36</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>239</v>
+        <v>206</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>240</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="36" t="s">
-        <v>263</v>
+        <v>230</v>
       </c>
       <c r="B16" s="36"/>
       <c r="C16" s="36"/>
@@ -4072,83 +4991,11 @@
       <c r="F16" s="36"/>
       <c r="G16" s="36"/>
     </row>
-    <row r="18" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-    </row>
-    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
-        <v>266</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-    </row>
-    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
-        <v>268</v>
-      </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-    </row>
-    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="3">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A23:G23"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4157,7 +5004,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4168,7 +5015,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>231</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4179,7 +5026,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4190,7 +5037,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>272</v>
+        <v>233</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4201,67 +5048,67 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>274</v>
+        <v>235</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>275</v>
+        <v>236</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>276</v>
+        <v>237</v>
       </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
     </row>
-    <row r="5" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>277</v>
+        <v>238</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>278</v>
+        <v>239</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>279</v>
+        <v>240</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>280</v>
+        <v>241</v>
       </c>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>287</v>
+        <v>248</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
@@ -4269,7 +5116,7 @@
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>288</v>
+        <v>249</v>
       </c>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -4280,7 +5127,7 @@
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>138</v>
+        <v>250</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>10</v>
@@ -4296,7 +5143,7 @@
         <v>91</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>289</v>
+        <v>251</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -4309,7 +5156,7 @@
         <v>91</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>290</v>
+        <v>252</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -4322,7 +5169,7 @@
         <v>91</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -4335,7 +5182,7 @@
         <v>91</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>292</v>
+        <v>254</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -4348,7 +5195,7 @@
         <v>91</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -4361,7 +5208,7 @@
         <v>91</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>294</v>
+        <v>256</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -4369,149 +5216,8 @@
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>299</v>
-      </c>
-      <c r="C22" s="8"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="8"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>301</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>303</v>
-      </c>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>305</v>
-      </c>
-      <c r="C28" s="8"/>
-      <c r="D28" s="8"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="8"/>
-    </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="15">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -4527,17 +5233,6 @@
     <mergeCell ref="B14:G14"/>
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="B16:G16"/>
-    <mergeCell ref="B17:G17"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="B20:G20"/>
-    <mergeCell ref="B21:G21"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B24:G24"/>
-    <mergeCell ref="B25:G25"/>
-    <mergeCell ref="B26:G26"/>
-    <mergeCell ref="B27:G27"/>
-    <mergeCell ref="B28:G28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4546,7 +5241,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -4557,7 +5252,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4568,7 +5263,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>307</v>
+        <v>258</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4579,7 +5274,7 @@
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>308</v>
+        <v>259</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4590,389 +5285,305 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>309</v>
+        <v>260</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>314</v>
+        <v>265</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>256</v>
+        <v>223</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
     </row>
-    <row r="7" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>313</v>
+        <v>264</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
+    <row r="9" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+    </row>
+    <row r="10" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>316</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="10" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-    </row>
-    <row r="12" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="B11" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-    </row>
-    <row r="13" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="B12" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>320</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B13" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-    </row>
-    <row r="15" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="B14" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7" t="s">
+        <v>260</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>322</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="B18" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B16" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
+      <c r="B19" s="8" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+    </row>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>325</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>309</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-    </row>
-    <row r="21" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+      <c r="B20" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>328</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-    </row>
-    <row r="23" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-    </row>
-    <row r="25" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D21" s="8"/>
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+    </row>
+    <row r="24" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>331</v>
+        <v>283</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>313</v>
+        <v>273</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
     </row>
-    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-    </row>
-    <row r="29" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-    </row>
-    <row r="30" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="8" t="s">
+      <c r="B26" s="8" t="s">
+        <v>284</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B30" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="D30" s="8"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-    </row>
-    <row r="31" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+      <c r="B27" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+    </row>
+    <row r="28" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-    </row>
-    <row r="32" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>323</v>
-      </c>
-      <c r="D32" s="8"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-    </row>
-    <row r="33" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-    </row>
-    <row r="34" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>256</v>
-      </c>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
+      <c r="B28" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="D28" s="8"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="25">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -4980,30 +5591,24 @@
     <mergeCell ref="C5:F5"/>
     <mergeCell ref="C6:F6"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="C10:F10"/>
     <mergeCell ref="C11:F11"/>
     <mergeCell ref="C12:F12"/>
     <mergeCell ref="C13:F13"/>
     <mergeCell ref="C14:F14"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="C16:F16"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="C19:F19"/>
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="C23:F23"/>
+    <mergeCell ref="A23:G23"/>
     <mergeCell ref="C24:F24"/>
     <mergeCell ref="C25:F25"/>
-    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
     <mergeCell ref="C28:F28"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C32:F32"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="C34:F34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5012,7 +5617,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -5023,7 +5628,7 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>287</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5034,7 +5639,7 @@
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>342</v>
+        <v>288</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5044,19 +5649,19 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="38" t="s">
-        <v>343</v>
-      </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
+      <c r="A3" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37"/>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>344</v>
+        <v>290</v>
       </c>
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
@@ -5067,177 +5672,177 @@
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>346</v>
+        <v>292</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>347</v>
+        <v>293</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>348</v>
+        <v>294</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>349</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>351</v>
-      </c>
-      <c r="D7" s="27" t="s">
-        <v>352</v>
-      </c>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
-        <v>353</v>
-      </c>
-      <c r="B8" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="C8" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="D8" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="31"/>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="26" t="s">
-        <v>357</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>358</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>359</v>
-      </c>
-      <c r="D9" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
-        <v>361</v>
-      </c>
-      <c r="B10" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>362</v>
-      </c>
-      <c r="D10" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>355</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="D11" s="27" t="s">
-        <v>366</v>
-      </c>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27"/>
-      <c r="G11" s="27"/>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="B12" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>368</v>
-      </c>
-      <c r="D12" s="31" t="s">
-        <v>369</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="31"/>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>370</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>350</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>365</v>
-      </c>
-      <c r="D13" s="27" t="s">
-        <v>371</v>
-      </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
-        <v>372</v>
-      </c>
-      <c r="B14" s="29" t="s">
-        <v>354</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="D14" s="31" t="s">
-        <v>373</v>
-      </c>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="26" t="s">
-        <v>374</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>375</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>376</v>
-      </c>
-      <c r="D15" s="27" t="s">
-        <v>377</v>
-      </c>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
+    <row r="7" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>297</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>298</v>
+      </c>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+    </row>
+    <row r="8" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>299</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D8" s="39" t="s">
+        <v>302</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>306</v>
+      </c>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+    </row>
+    <row r="10" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>297</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="39" t="s">
+        <v>309</v>
+      </c>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
+      <c r="G10" s="39"/>
+    </row>
+    <row r="11" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>301</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="E11" s="38"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="38"/>
+    </row>
+    <row r="12" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>304</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" s="39" t="s">
+        <v>315</v>
+      </c>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+    </row>
+    <row r="13" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>311</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>317</v>
+      </c>
+      <c r="E13" s="38"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="38"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="20" t="s">
+        <v>318</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="D14" s="39" t="s">
+        <v>319</v>
+      </c>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+    </row>
+    <row r="15" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>322</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>323</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -5251,17 +5856,17 @@
         <v>96</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>379</v>
+        <v>325</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>380</v>
+        <v>326</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
-    <row r="19" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>91</v>
       </c>
@@ -5269,193 +5874,105 @@
         <v>117</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
     </row>
-    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>382</v>
+        <v>328</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>384</v>
+        <v>330</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
     </row>
-    <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>385</v>
+        <v>331</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>381</v>
+        <v>327</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
     </row>
-    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>386</v>
+        <v>332</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
     </row>
-    <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
         <v>91</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>387</v>
+        <v>333</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>388</v>
+        <v>334</v>
       </c>
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="8"/>
       <c r="G24" s="8"/>
     </row>
-    <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>91</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>389</v>
+        <v>335</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>383</v>
+        <v>329</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="4"/>
     </row>
-    <row r="27" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="39" t="s">
-        <v>390</v>
-      </c>
-      <c r="B27" s="39"/>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
-      <c r="F27" s="39"/>
-      <c r="G27" s="39"/>
-    </row>
-    <row r="28" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>391</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-    </row>
-    <row r="29" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-    </row>
-    <row r="30" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>393</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-    </row>
-    <row r="31" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="34" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" ht="40" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="40" t="s">
-        <v>397</v>
-      </c>
-      <c r="B35" s="40"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="40"/>
-      <c r="E35" s="40"/>
-      <c r="F35" s="40"/>
-      <c r="G35" s="40"/>
-    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="23">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A3:G3"/>
@@ -5479,14 +5996,392 @@
     <mergeCell ref="C23:G23"/>
     <mergeCell ref="C24:G24"/>
     <mergeCell ref="C25:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A34:G34"/>
-    <mergeCell ref="A35:G35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="38" customWidth="1"/>
+    <col min="5" max="7" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="40">
+        <v>1</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+    </row>
+    <row r="8" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="43">
+        <v>2</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="45" t="s">
+        <v>348</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>349</v>
+      </c>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+    </row>
+    <row r="9" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="40">
+        <v>3</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>350</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>351</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>352</v>
+      </c>
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+    </row>
+    <row r="10" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="43">
+        <v>4</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>353</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>354</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>355</v>
+      </c>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+    </row>
+    <row r="11" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="40">
+        <v>5</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" s="42" t="s">
+        <v>358</v>
+      </c>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+    </row>
+    <row r="12" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="43">
+        <v>6</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" s="45" t="s">
+        <v>360</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+    </row>
+    <row r="13" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="40">
+        <v>7</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>362</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>363</v>
+      </c>
+      <c r="D13" s="42" t="s">
+        <v>364</v>
+      </c>
+      <c r="E13" s="42"/>
+      <c r="F13" s="42"/>
+      <c r="G13" s="42"/>
+    </row>
+    <row r="14" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="43">
+        <v>8</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="C14" s="45" t="s">
+        <v>366</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>367</v>
+      </c>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="45"/>
+    </row>
+    <row r="15" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="40">
+        <v>9</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>368</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>369</v>
+      </c>
+      <c r="D15" s="42" t="s">
+        <v>370</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+    </row>
+    <row r="16" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="43">
+        <v>10</v>
+      </c>
+      <c r="B16" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="C16" s="45" t="s">
+        <v>372</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>373</v>
+      </c>
+      <c r="E16" s="45"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="45"/>
+    </row>
+    <row r="17" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="40">
+        <v>11</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>374</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>375</v>
+      </c>
+      <c r="D17" s="42" t="s">
+        <v>376</v>
+      </c>
+      <c r="E17" s="42"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="42"/>
+    </row>
+    <row r="18" ht="70" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="43">
+        <v>12</v>
+      </c>
+      <c r="B18" s="44" t="s">
+        <v>377</v>
+      </c>
+      <c r="C18" s="45" t="s">
+        <v>378</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="E18" s="45"/>
+      <c r="F18" s="45"/>
+      <c r="G18" s="45"/>
+    </row>
+    <row r="20" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>382</v>
+      </c>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>384</v>
+      </c>
+      <c r="B24" s="46"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="46"/>
+      <c r="E24" s="46"/>
+      <c r="F24" s="46"/>
+      <c r="G24" s="46"/>
+    </row>
+    <row r="25" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="46" t="s">
+        <v>386</v>
+      </c>
+      <c r="B26" s="46"/>
+      <c r="C26" s="46"/>
+      <c r="D26" s="46"/>
+      <c r="E26" s="46"/>
+      <c r="F26" s="46"/>
+      <c r="G26" s="46"/>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="D6:G6"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D8:G8"/>
+    <mergeCell ref="D9:G9"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D12:G12"/>
+    <mergeCell ref="D13:G13"/>
+    <mergeCell ref="D14:G14"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="D16:G16"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A26:G26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
